--- a/s121_emp_df_class.xlsx
+++ b/s121_emp_df_class.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,30 +485,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>LineID</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MonthOTNew</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTDOTAvgNew</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>OJTCode</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>SkillName</t>
         </is>
@@ -517,7 +522,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>85704769</t>
+          <t>88441164</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -532,7 +537,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,48 +557,53 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>BSFA12</t>
+          <t>BSTesting11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M2" t="n">
-        <v>40</v>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N2" t="n">
-        <v>27.33</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>OJT3116</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="O2" t="n">
+        <v>25.33</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ECU VI</t>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>88786791</t>
+          <t>88441164</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -608,7 +618,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -628,48 +638,53 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="M3" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N3" t="n">
         <v>16</v>
       </c>
-      <c r="N3" t="n">
-        <v>30.17</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>OJT3126</t>
-        </is>
+      <c r="O3" t="n">
+        <v>25.33</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>88786791</t>
+          <t>88441164</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -684,7 +699,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -704,48 +719,53 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="M4" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N4" t="n">
         <v>16</v>
       </c>
-      <c r="N4" t="n">
-        <v>30.17</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>OJT3262</t>
-        </is>
+      <c r="O4" t="n">
+        <v>25.33</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>FA ML</t>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>88786791</t>
+          <t>88441164</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -760,7 +780,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -780,39 +800,44 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="M5" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N5" t="n">
         <v>16</v>
       </c>
-      <c r="N5" t="n">
-        <v>30.17</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>OJT3124</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Material Handling</t>
         </is>
@@ -821,7 +846,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>88786791</t>
+          <t>85107824</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -836,61 +861,3873 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BSTesting14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>85107824</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BSTesting14</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N7" t="n">
+        <v>28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>OJT3105</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Kardex_Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>85107824</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BSTesting14</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N8" t="n">
+        <v>28</v>
+      </c>
+      <c r="O8" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>85107824</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BSTesting14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N9" t="n">
+        <v>28</v>
+      </c>
+      <c r="O9" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>85734228</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>BSTesting06</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N10" t="n">
+        <v>57</v>
+      </c>
+      <c r="O10" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>85474428</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>S121</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ME/MOE6-CN</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ME/MFO6.5-CN</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BSTesting09</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N11" t="n">
+        <v>31</v>
+      </c>
+      <c r="O11" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>85474428</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BSTesting09</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N12" t="n">
+        <v>31</v>
+      </c>
+      <c r="O12" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>85145034</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>BSFA14</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BSTesting05</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="M13" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N13" t="n">
+        <v>44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>85145034</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>BSTesting05</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N14" t="n">
+        <v>44</v>
+      </c>
+      <c r="O14" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>OJT3271</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Offline cleaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>85283651</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>BSTesting15</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12</v>
+      </c>
+      <c r="O15" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>85283651</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>BSTesting15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12</v>
+      </c>
+      <c r="O16" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>85283651</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>BSTesting15</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N17" t="n">
+        <v>12</v>
+      </c>
+      <c r="O17" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>88717624</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N18" t="n">
+        <v>52</v>
+      </c>
+      <c r="O18" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>88717624</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N19" t="n">
+        <v>52</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>88717624</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N20" t="n">
+        <v>52</v>
+      </c>
+      <c r="O20" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>OJT3105</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Kardex_Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>85900182</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N21" t="n">
+        <v>46</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>85900182</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N22" t="n">
+        <v>46</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>OJT0966</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ME CN Plant common skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>85900191</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N23" t="n">
+        <v>58</v>
+      </c>
+      <c r="O23" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>85900191</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N24" t="n">
+        <v>58</v>
+      </c>
+      <c r="O24" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>85900191</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N25" t="n">
+        <v>58</v>
+      </c>
+      <c r="O25" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>OJT0966</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ME CN Plant common skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>85900244</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N26" t="n">
+        <v>62</v>
+      </c>
+      <c r="O26" t="n">
         <v>16</v>
       </c>
-      <c r="N6" t="n">
-        <v>30.17</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>OJT3132</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Lid and Hu sealing</t>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>85900244</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N27" t="n">
+        <v>62</v>
+      </c>
+      <c r="O27" t="n">
+        <v>16</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>85900244</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N28" t="n">
+        <v>62</v>
+      </c>
+      <c r="O28" t="n">
+        <v>16</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>OJT0966</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ME CN Plant common skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>88483396</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N29" t="n">
+        <v>36</v>
+      </c>
+      <c r="O29" t="n">
+        <v>24</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>OJT3212</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Testing Foreman</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>88310992</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N30" t="n">
+        <v>13</v>
+      </c>
+      <c r="O30" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>88310992</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13</v>
+      </c>
+      <c r="O31" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>88797217</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N32" t="n">
+        <v>64</v>
+      </c>
+      <c r="O32" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>88797217</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N33" t="n">
+        <v>64</v>
+      </c>
+      <c r="O33" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>OJT3254</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Testing LL</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>88797217</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N34" t="n">
+        <v>64</v>
+      </c>
+      <c r="O34" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>OJT3105</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Kardex_Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>88797217</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N35" t="n">
+        <v>64</v>
+      </c>
+      <c r="O35" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>88797217</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N36" t="n">
+        <v>64</v>
+      </c>
+      <c r="O36" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>88797217</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N37" t="n">
+        <v>64</v>
+      </c>
+      <c r="O37" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>OJT3260</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>PCBA VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>89086652</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>89086652</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>OJT3260</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>PCBA VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>89192984</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>BSTesting15</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N40" t="n">
+        <v>9</v>
+      </c>
+      <c r="O40" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>89192984</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>BSTesting15</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N41" t="n">
+        <v>9</v>
+      </c>
+      <c r="O41" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>89192984</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>BSTesting15</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N42" t="n">
+        <v>9</v>
+      </c>
+      <c r="O42" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>OJT3260</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>PCBA VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>89198764</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>BSTesting07</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N43" t="n">
+        <v>22</v>
+      </c>
+      <c r="O43" t="n">
+        <v>32</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>89207095</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N44" t="n">
+        <v>53</v>
+      </c>
+      <c r="O44" t="n">
+        <v>31</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>89207095</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N45" t="n">
+        <v>53</v>
+      </c>
+      <c r="O45" t="n">
+        <v>31</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>89207095</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N46" t="n">
+        <v>53</v>
+      </c>
+      <c r="O46" t="n">
+        <v>31</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>89209743</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>BSTesting08</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N47" t="n">
+        <v>58</v>
+      </c>
+      <c r="O47" t="n">
+        <v>32</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>88598487</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O48" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>88598487</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O49" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>88598487</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O50" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>88598487</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O51" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>OJT3105</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Kardex_Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>88610793</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N52" t="n">
+        <v>32</v>
+      </c>
+      <c r="O52" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>88610793</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N53" t="n">
+        <v>32</v>
+      </c>
+      <c r="O53" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>

--- a/s121_emp_df_class.xlsx
+++ b/s121_emp_df_class.xlsx
@@ -522,7 +522,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>88441164</t>
+          <t>85107824</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -567,24 +567,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>BSTesting11</t>
+          <t>BSTesting14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O2" t="n">
         <v>25.33</v>
@@ -603,7 +603,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>88441164</t>
+          <t>85107824</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -648,43 +648,43 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>BSTesting11</t>
+          <t>BSTesting14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
         <v>25.33</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3105</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Kardex_Testing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>88441164</t>
+          <t>85107824</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -729,43 +729,43 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>BSTesting11</t>
+          <t>BSTesting14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O4" t="n">
         <v>25.33</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>88441164</t>
+          <t>85107824</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -810,24 +810,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>BSTesting11</t>
+          <t>BSTesting14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O5" t="n">
         <v>25.33</v>
@@ -846,7 +846,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>85107824</t>
+          <t>85474428</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -891,43 +891,43 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BSTesting14</t>
+          <t>BSTesting09</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O6" t="n">
-        <v>25.33</v>
+        <v>30.33</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>OJT3632</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Testing OP(Auto line)</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>85107824</t>
+          <t>85474428</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -972,43 +972,43 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BSTesting14</t>
+          <t>BSTesting09</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>25.33</v>
+        <v>30.33</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>OJT3105</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Kardex_Testing</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>85107824</t>
+          <t>85145034</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1048,48 +1048,48 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BSTesting14</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N8" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>25.33</v>
+        <v>29.33</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>85107824</t>
+          <t>85145034</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1129,48 +1129,48 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BSTesting14</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N9" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>25.33</v>
+        <v>29.33</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>OJT3124</t>
+          <t>OJT3271</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>Offline cleaning</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>85734228</t>
+          <t>85283651</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1210,48 +1210,48 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>BSTesting06</t>
+          <t>BSTesting15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N10" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>33.67</v>
+        <v>34.67</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3632</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>85474428</t>
+          <t>85283651</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,43 +1296,43 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BSTesting09</t>
+          <t>BSTesting15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N11" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>30.33</v>
+        <v>34.67</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>85474428</t>
+          <t>85283651</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,43 +1377,43 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BSTesting09</t>
+          <t>BSTesting15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N12" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>30.33</v>
+        <v>34.67</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>85145034</t>
+          <t>88717624</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1453,48 +1453,48 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BSTesting05</t>
+          <t>BSFA02</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N13" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O13" t="n">
-        <v>29.33</v>
+        <v>18.67</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3124</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>85145034</t>
+          <t>88717624</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1534,48 +1534,48 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BSTesting05</t>
+          <t>BSFA02</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N14" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O14" t="n">
-        <v>29.33</v>
+        <v>18.67</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>OJT3271</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Offline cleaning</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>85283651</t>
+          <t>88717624</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BSTesting15</t>
+          <t>BSFA02</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1637,26 +1637,26 @@
         <v>46108</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="O15" t="n">
-        <v>34.67</v>
+        <v>18.67</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>OJT3632</t>
+          <t>OJT3105</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Testing OP(Auto line)</t>
+          <t>Kardex_Testing</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>85283651</t>
+          <t>85734228</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1696,48 +1696,48 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>BSTesting15</t>
+          <t>BSTesting06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="O16" t="n">
-        <v>34.67</v>
+        <v>33.67</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>85283651</t>
+          <t>85900182</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>BSTesting15</t>
+          <t>BSFA02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="O17" t="n">
-        <v>34.67</v>
+        <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>88717624</t>
+          <t>85900182</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1873,33 +1873,33 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N18" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O18" t="n">
-        <v>18.67</v>
+        <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>OJT3124</t>
+          <t>OJT0966</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>ME CN Plant common skill</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>88717624</t>
+          <t>85900191</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1954,17 +1954,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N19" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O19" t="n">
-        <v>18.67</v>
+        <v>24.67</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>88717624</t>
+          <t>85900191</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2035,33 +2035,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N20" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O20" t="n">
-        <v>18.67</v>
+        <v>24.67</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>OJT3105</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Kardex_Testing</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>85900182</t>
+          <t>85900191</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2123,26 +2123,26 @@
         <v>46108</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>24.67</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT0966</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>ME CN Plant common skill</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>85900182</t>
+          <t>85900244</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2204,26 +2204,26 @@
         <v>46108</v>
       </c>
       <c r="N22" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>OJT0966</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ME CN Plant common skill</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>85900191</t>
+          <t>85900244</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2285,26 +2285,26 @@
         <v>46108</v>
       </c>
       <c r="N23" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O23" t="n">
-        <v>24.67</v>
+        <v>16</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>85900191</t>
+          <t>85900244</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2366,26 +2366,26 @@
         <v>46108</v>
       </c>
       <c r="N24" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O24" t="n">
-        <v>24.67</v>
+        <v>16</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT0966</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>ME CN Plant common skill</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>85900191</t>
+          <t>88483396</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2430,43 +2430,43 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>BSFA02</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>Shopfloor leader</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N25" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="O25" t="n">
-        <v>24.67</v>
+        <v>24</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>OJT0966</t>
+          <t>OJT3212</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>ME CN Plant common skill</t>
+          <t>Testing Foreman</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>85900244</t>
+          <t>88797217</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2511,43 +2511,43 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>BSFA02</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>Shopfloor leader</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N26" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>28.67</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3124</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>85900244</t>
+          <t>88797217</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2592,43 +2592,43 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>BSFA02</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>Shopfloor leader</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N27" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>28.67</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3254</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Testing LL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>85900244</t>
+          <t>88797217</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,43 +2673,43 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>BSFA02</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>Shopfloor leader</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N28" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>28.67</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>OJT0966</t>
+          <t>OJT3105</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>ME CN Plant common skill</t>
+          <t>Kardex_Testing</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>88483396</t>
+          <t>88797217</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2771,26 +2771,26 @@
         <v>46108</v>
       </c>
       <c r="N29" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="O29" t="n">
-        <v>24</v>
+        <v>28.67</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>OJT3212</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Testing Foreman</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>88310992</t>
+          <t>88797217</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2830,48 +2830,48 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>BSTesting01</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>Shopfloor leader</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="O30" t="n">
-        <v>31.33</v>
+        <v>28.67</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>OJT3124</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>88310992</t>
+          <t>88797217</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2911,48 +2911,48 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>BSTesting01</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>Shopfloor leader</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N31" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="O31" t="n">
-        <v>31.33</v>
+        <v>28.67</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3260</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>PCBA VI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>88797217</t>
+          <t>88310992</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2992,32 +2992,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BSTesting01</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Shopfloor leader</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N32" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="O32" t="n">
-        <v>28.67</v>
+        <v>31.33</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>88797217</t>
+          <t>88310992</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3073,48 +3073,48 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BSTesting01</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Shopfloor leader</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N33" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="O33" t="n">
-        <v>28.67</v>
+        <v>31.33</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>OJT3254</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Testing LL</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>88797217</t>
+          <t>88441164</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3159,43 +3159,43 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BSTesting11</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Shopfloor leader</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N34" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="O34" t="n">
-        <v>28.67</v>
+        <v>25.33</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>OJT3105</t>
+          <t>OJT3632</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Kardex_Testing</t>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>88797217</t>
+          <t>88441164</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3240,27 +3240,27 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BSTesting11</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Shopfloor leader</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N35" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="O35" t="n">
-        <v>28.67</v>
+        <v>25.33</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>88797217</t>
+          <t>88441164</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3321,27 +3321,27 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BSTesting11</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Shopfloor leader</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N36" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="O36" t="n">
-        <v>28.67</v>
+        <v>25.33</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>88797217</t>
+          <t>88441164</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3402,36 +3402,36 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>BSTesting11</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Shopfloor leader</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N37" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="O37" t="n">
-        <v>28.67</v>
+        <v>25.33</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>OJT3260</t>
+          <t>OJT3124</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>PCBA VI</t>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>89198764</t>
+          <t>88598487</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3883,17 +3883,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>BSTesting07</t>
+          <t>BSTesting01</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3905,26 +3905,26 @@
         <v>46108</v>
       </c>
       <c r="N43" t="n">
-        <v>22</v>
+        <v>-8</v>
       </c>
       <c r="O43" t="n">
-        <v>32</v>
+        <v>34.67</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3124</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>89207095</t>
+          <t>88598487</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>BSTesting17</t>
+          <t>BSTesting01</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3986,26 +3986,26 @@
         <v>46108</v>
       </c>
       <c r="N44" t="n">
-        <v>53</v>
+        <v>-8</v>
       </c>
       <c r="O44" t="n">
-        <v>31</v>
+        <v>34.67</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>OJT3632</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Testing OP(Auto line)</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>89207095</t>
+          <t>88598487</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>BSTesting17</t>
+          <t>BSTesting01</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4067,26 +4067,26 @@
         <v>46108</v>
       </c>
       <c r="N45" t="n">
-        <v>53</v>
+        <v>-8</v>
       </c>
       <c r="O45" t="n">
-        <v>31</v>
+        <v>34.67</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>89207095</t>
+          <t>88598487</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>BSTesting17</t>
+          <t>BSTesting01</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4148,26 +4148,26 @@
         <v>46108</v>
       </c>
       <c r="N46" t="n">
-        <v>53</v>
+        <v>-8</v>
       </c>
       <c r="O46" t="n">
-        <v>31</v>
+        <v>34.67</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3105</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Kardex_Testing</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>89209743</t>
+          <t>88610793</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4207,17 +4207,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>BSTesting08</t>
+          <t>BSFA02</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4229,26 +4229,26 @@
         <v>46108</v>
       </c>
       <c r="N47" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="O47" t="n">
-        <v>32</v>
+        <v>23.33</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3632</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>88598487</t>
+          <t>88610793</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>BSTesting01</t>
+          <t>BSFA02</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4310,26 +4310,26 @@
         <v>46108</v>
       </c>
       <c r="N48" t="n">
-        <v>-8</v>
+        <v>32</v>
       </c>
       <c r="O48" t="n">
-        <v>34.67</v>
+        <v>23.33</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>OJT3124</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>88598487</t>
+          <t>89198764</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>BSTesting01</t>
+          <t>BSTesting07</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4391,26 +4391,26 @@
         <v>46108</v>
       </c>
       <c r="N49" t="n">
-        <v>-8</v>
+        <v>22</v>
       </c>
       <c r="O49" t="n">
-        <v>34.67</v>
+        <v>32</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>88598487</t>
+          <t>89207095</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>BSTesting01</t>
+          <t>BSTesting17</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4472,26 +4472,26 @@
         <v>46108</v>
       </c>
       <c r="N50" t="n">
-        <v>-8</v>
+        <v>53</v>
       </c>
       <c r="O50" t="n">
-        <v>34.67</v>
+        <v>31</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3632</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>88598487</t>
+          <t>89207095</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>BSTesting01</t>
+          <t>BSTesting17</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4553,26 +4553,26 @@
         <v>46108</v>
       </c>
       <c r="N51" t="n">
-        <v>-8</v>
+        <v>53</v>
       </c>
       <c r="O51" t="n">
-        <v>34.67</v>
+        <v>31</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>OJT3105</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Kardex_Testing</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>88610793</t>
+          <t>89207095</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>BSFA02</t>
+          <t>BSTesting17</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4634,26 +4634,26 @@
         <v>46108</v>
       </c>
       <c r="N52" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="O52" t="n">
-        <v>23.33</v>
+        <v>31</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>OJT3632</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Testing OP(Auto line)</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>88610793</t>
+          <t>89209743</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4693,17 +4693,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>BSFA02</t>
+          <t>BSTesting08</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4715,19 +4715,19 @@
         <v>46108</v>
       </c>
       <c r="N53" t="n">
+        <v>58</v>
+      </c>
+      <c r="O53" t="n">
         <v>32</v>
       </c>
-      <c r="O53" t="n">
-        <v>23.33</v>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
